--- a/result/icd9_inclusion_mapping_summary_TFIDF.xlsx
+++ b/result/icd9_inclusion_mapping_summary_TFIDF.xlsx
@@ -451,13 +451,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="75" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="75" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -544,7 +544,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>079</t>
+          <t>0799</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1755, 1753, 1754</t>
+          <t>1753, 1755, 1754</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1755, 1753, 1754</t>
+          <t>1753, 1755, 1754</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1755, 1753, 1754</t>
+          <t>1753, 1755, 1754</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>2049</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>2049</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>2049</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>operations on: submaxillary gland and duct</t>
+          <t>operations on: parotid gland and duct</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -705,66 +705,66 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operations on pharynx</t>
+          <t>Operations on salivary glands and ducts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>operations on: hypopharynx</t>
+          <t>operations on: sublingual gland and duct</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2699</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operations on pharynx</t>
+          <t>Operations on salivary glands and ducts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>operations on: nasopharynx</t>
+          <t>operations on: submaxillary gland and duct</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2699</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operations on pharynx</t>
+          <t>Other operations on mouth and face</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>operations on: oropharynx</t>
+          <t>operations on: palate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2799</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>operations on: pyriform sinus</t>
+          <t>operations on: hypopharynx</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -793,196 +793,702 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Central venous catheter placement with guidance</t>
+          <t>Operations on pharynx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>electrocardiogram</t>
+          <t>operations on: nasopharynx</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>2999</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operations on appendix</t>
+          <t>Operations on pharynx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>appendiceal stump</t>
+          <t>operations on: oropharynx</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>2999</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Incision or excision of perirectal tissue or lesion</t>
+          <t>Operations on pharynx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pelvirectal tissue</t>
+          <t>operations on: pyriform sinus</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>2999</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operations on gallbladder and biliary tract</t>
+          <t>Insertion of percutaneous external heart assist device</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>operations on: sphincter of Oddi</t>
+          <t>Extrinsic heart assist device</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>9744</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operations on urethra</t>
+          <t>Insertion of percutaneous external heart assist device</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>operations on: periurethral tissue</t>
+          <t>Percutaneous heart assist device</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>9744</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Repair of the anulus fibrosus with graft or prosthesis</t>
+          <t>Central venous catheter placement with guidance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>microsurgical suture repair with fascial autograft</t>
+          <t>electrocardiogram</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>8054</t>
+          <t>8952</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Phlebography</t>
+          <t>Operations on appendix</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>retrograde phlebography</t>
+          <t>appendiceal stump</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>4709</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>488</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Diagnostic ultrasound</t>
+          <t>Incision or excision of perirectal tissue or lesion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Non-invasive ultrasound</t>
+          <t>pelvirectal tissue</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>4882</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>488</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Incision or excision of perirectal tissue or lesion</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>rectovaginal septum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4882, 4881</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Operations on gallbladder and biliary tract</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>operations on: sphincter of Oddi</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5189</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Other operations on abdominal region</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>operations on: mesentery</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Other operations on abdominal region</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>operations on: omentum</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Other operations on abdominal region</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>operations on: peritoneum</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Operations on urethra</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>operations on: periurethral tissue</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bilateral endoscopic destruction or occlusion of fallopian tubes</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>bilateral endoscopic destruction or occlusion of fallopian tubes by: culdoscopy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bilateral endoscopic destruction or occlusion of fallopian tubes</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>bilateral endoscopic destruction or occlusion of fallopian tubes by: endoscopy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bilateral endoscopic destruction or occlusion of fallopian tubes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>bilateral endoscopic destruction or occlusion of fallopian tubes by: hysteroscopy</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bilateral endoscopic destruction or occlusion of fallopian tubes</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>bilateral endoscopic destruction or occlusion of fallopian tubes by: laparoscopy</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bilateral endoscopic destruction or occlusion of fallopian tubes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bilateral endoscopic destruction or occlusion of fallopian tubes by: peritoneoscopy</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Reduction of fracture and dislocation</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>application of cast or splint</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>9354</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Incision and excision of joint structures</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>operations on: ligament</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>8199</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>8053</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Repair of the anulus fibrosus with graft or prosthesis</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>microsurgical suture repair with fascial autograft</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8054</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8460</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Insertion of spinal disc prosthesis, not otherwise specified</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8461</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Insertion of partial spinal disc prosthesis, cervical</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8462</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Insertion of total spinal disc prosthesis, cervical</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Insertion of spinal disc prosthesis, thoracic</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8464</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Insertion of partial spinal disc prosthesis, lumbosacral</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8465</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Insertion of total spinal disc prosthesis, lumbosacral</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>diskectomy (discectomy)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>8051</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Phlebography</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>retrograde phlebography</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8860, 8861, 8864, 8866</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Diagnostic ultrasound</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Non-invasive ultrasound</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>8872</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Diagnostic ultrasound</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ultrasonography</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8872, 8873, 9513</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>967</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Other continuous invasive mechanical ventilation</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Endotracheal respiratory assistance</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>3961</t>
         </is>
